--- a/branches/release/2027.0.0-ballot.rc1/StructureDefinition-mii-pr-molgen-empfohlene-folgemassnahme.xlsx
+++ b/branches/release/2027.0.0-ballot.rc1/StructureDefinition-mii-pr-molgen-empfohlene-folgemassnahme.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T09:30:27+00:00</t>
+    <t>2026-09-02T09:55:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release/2027.0.0-ballot.rc1/StructureDefinition-mii-pr-molgen-empfohlene-folgemassnahme.xlsx
+++ b/branches/release/2027.0.0-ballot.rc1/StructureDefinition-mii-pr-molgen-empfohlene-folgemassnahme.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T09:55:35+00:00</t>
+    <t>2026-09-03T08:56:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
